--- a/public/xlsx/edificio22.xlsx
+++ b/public/xlsx/edificio22.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\bbsbase\public\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\mylab\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -7842,9 +7842,6 @@
       <c r="I5" t="s">
         <v>20</v>
       </c>
-      <c r="J5">
-        <v>1251</v>
-      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -7874,9 +7871,6 @@
       <c r="I6" t="s">
         <v>20</v>
       </c>
-      <c r="J6">
-        <v>1252</v>
-      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -7906,9 +7900,6 @@
       <c r="I7" t="s">
         <v>20</v>
       </c>
-      <c r="J7">
-        <v>1253</v>
-      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -7938,9 +7929,6 @@
       <c r="I8" t="s">
         <v>20</v>
       </c>
-      <c r="J8">
-        <v>1254</v>
-      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -7970,9 +7958,6 @@
       <c r="I9" t="s">
         <v>20</v>
       </c>
-      <c r="J9">
-        <v>1255</v>
-      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -8002,9 +7987,6 @@
       <c r="I10" t="s">
         <v>20</v>
       </c>
-      <c r="J10">
-        <v>1256</v>
-      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -8034,9 +8016,6 @@
       <c r="I11" t="s">
         <v>20</v>
       </c>
-      <c r="J11">
-        <v>1257</v>
-      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -8066,9 +8045,6 @@
       <c r="I12" t="s">
         <v>20</v>
       </c>
-      <c r="J12">
-        <v>1258</v>
-      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -8097,9 +8073,6 @@
       </c>
       <c r="I13" t="s">
         <v>20</v>
-      </c>
-      <c r="J13">
-        <v>1259</v>
       </c>
     </row>
   </sheetData>
